--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
   </si>
 </sst>
 </file>
@@ -857,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -887,6 +896,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,10 +85,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MATA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CRISTIAN ARTURO</t>
   </si>
   <si>
     <t>ESMERALDA</t>
@@ -866,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -898,24 +907,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920126</v>
+        <v>20330051920172</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920126</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -524,10 +524,10 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -536,7 +536,7 @@
         <v>26</v>
       </c>
       <c r="G3">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -664,10 +664,10 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>29</v>
@@ -798,10 +798,10 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -810,7 +810,7 @@
         <v>26</v>
       </c>
       <c r="G3">
-        <v>89.66</v>
+        <v>86.67</v>
       </c>
       <c r="H3">
         <v>8.199999999999999</v>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,19 +88,10 @@
     <t>MATA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CANSECO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
   </si>
 </sst>
 </file>
@@ -498,10 +489,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -510,7 +501,7 @@
         <v>30</v>
       </c>
       <c r="G2">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
         <v>7.8</v>
@@ -641,10 +632,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>33</v>
@@ -772,10 +763,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -784,7 +775,7 @@
         <v>30</v>
       </c>
       <c r="G2">
-        <v>90.91</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2">
         <v>7.9</v>
@@ -875,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -913,10 +904,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -925,30 +916,7 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920126</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
   </si>
 </sst>
 </file>
@@ -492,19 +483,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -518,10 +509,10 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>26</v>
@@ -530,7 +521,7 @@
         <v>86.67</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -635,16 +626,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -658,16 +652,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -681,16 +678,19 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>36</v>
       </c>
-      <c r="E4">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,16 +704,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.31999999999999</v>
+      </c>
+      <c r="H5">
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -766,10 +769,10 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -778,7 +781,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -792,19 +795,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>86.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>9.1</v>
@@ -856,7 +859,7 @@
         <v>90.31999999999999</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -896,29 +899,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920172</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,42 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -798,16 +834,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>76.67</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,7 +869,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,16 +886,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +905,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -899,6 +935,98 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920031</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920036</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920048</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>COMIHUA</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
   </si>
   <si>
     <t>ALEJANDRO GABRIEL</t>
@@ -905,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -937,16 +928,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920031</v>
+        <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -960,16 +951,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>21330051920048</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -983,47 +974,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920048</v>
+        <v>20330051920132</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920132</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
         <v>2</v>
       </c>
     </row>
